--- a/Data/Config.xlsx
+++ b/Data/Config.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Asus\Documents\UiPath\NH02_ProcessNewEmployee\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4BC081F-1526-4000-9507-1A0FA60C135C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C787EFC5-1F95-4004-B1C8-5E524CC4D072}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="22935" yWindow="3300" windowWidth="26865" windowHeight="15345" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="45">
   <si>
     <t>Name</t>
   </si>
@@ -160,12 +160,6 @@
   </si>
   <si>
     <t>ProcessEmployee</t>
-  </si>
-  <si>
-    <t>ProcessTestMode</t>
-  </si>
-  <si>
-    <t>TestModeUser</t>
   </si>
 </sst>
 </file>
@@ -2822,21 +2816,10 @@
       <c r="Z1" s="1"/>
     </row>
     <row r="2" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A2" s="3" t="s">
-        <v>45</v>
-      </c>
-      <c r="B2" s="3" t="s">
-        <v>45</v>
-      </c>
+      <c r="A2" s="3"/>
+      <c r="B2" s="3"/>
     </row>
-    <row r="3" spans="1:26" ht="14.25" customHeight="1">
-      <c r="A3" t="s">
-        <v>46</v>
-      </c>
-      <c r="B3" t="s">
-        <v>46</v>
-      </c>
-    </row>
+    <row r="3" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="4" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="5" spans="1:26" ht="14.25" customHeight="1"/>
     <row r="6" spans="1:26" ht="14.25" customHeight="1"/>
